--- a/UTCUTS/A2_Structure_Lists.xlsx
+++ b/UTCUTS/A2_Structure_Lists.xlsx
@@ -3556,7 +3556,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4494083-1ABC-479E-AE05-7B75C6BF26AE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2786BDC0-577A-4EB3-A363-A4FAFB7BFC3C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
